--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Prod.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="109">
   <si>
     <t>Result</t>
   </si>
@@ -319,6 +319,51 @@
   </si>
   <si>
     <t>Thu Jul 09 11:52:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:51:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:52:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:54:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:54:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:55:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:57:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:58:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 02:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 02:00:55 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1031,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>33</v>
@@ -1025,7 +1070,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>44</v>
@@ -1066,7 +1111,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>45</v>
@@ -1107,7 +1152,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>49</v>
@@ -1172,7 +1217,7 @@
         <v>47</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>50</v>
@@ -1384,7 +1429,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s" s="5">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>27</v>
@@ -1428,7 +1473,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>30</v>
@@ -1499,7 +1544,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>31</v>
@@ -1540,7 +1585,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s" s="5">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>32</v>
@@ -1582,7 +1627,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s" s="5">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>46</v>
